--- a/SHINHWA_QMS_WORKFLOW/99_산출물/작성요청_파일_20261029_v3/04_메시지_발송일정표_20261029_v8.xlsx
+++ b/SHINHWA_QMS_WORKFLOW/99_산출물/작성요청_파일_20261029_v3/04_메시지_발송일정표_20261029_v8.xlsx
@@ -2015,7 +2015,7 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>한상돈 부장</t>
+          <t>한상돈 부장 님</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>SH-FM-208_기준값확인_20261028/메시지_한상돈_SH-FM-208_기준값확인_20261028.txt</t>
+          <t>발송용_호칭반영_20261029/메시지_한상돈부장_SH-FM-208_기준값확인_20261029.txt</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>한상돈 님</t>
+          <t>한상돈 부장 님</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>발송용_일정방안A반영_20261029/재요청_메시지_한상돈_회신재요청_20261028_일정방안A.txt</t>
+          <t>발송용_호칭반영_20261029/재요청_메시지_한상돈부장_회신재요청_일정방안A_20261029.txt</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
